--- a/tests/fixtures/seguimiento_maduracion_sample.xlsx
+++ b/tests/fixtures/seguimiento_maduracion_sample.xlsx
@@ -404,7 +404,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>SEGUIMIENTO DE MADURACIÓN   FL 8.5.1  REV 5</v>
+        <v>SEGUIMIENTO DE MADURACIÓN VENDIMIA 2026   FL 8.5.1  REV 5</v>
       </c>
     </row>
     <row r="3">

--- a/tests/fixtures/seguimiento_maduracion_sample.xlsx
+++ b/tests/fixtures/seguimiento_maduracion_sample.xlsx
@@ -481,7 +481,7 @@
         <v>06.07</v>
       </c>
       <c r="R6" s="1">
-        <v>7</v>
+        <v>7.07</v>
       </c>
       <c r="S6" t="str">
         <v>08.07</v>
